--- a/2-base-dados/Entregaveis Finais/VoltGo-DicionarioDados.xlsx
+++ b/2-base-dados/Entregaveis Finais/VoltGo-DicionarioDados.xlsx
@@ -19,12 +19,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="429">
   <si>
     <t>VoltGo — Dicionário de Dados</t>
   </si>
   <si>
-    <t>Gerado a partir do esquema real da base de dados VoltGo, depois de os scripts terem sido executados e testados.</t>
+    <t>Gerado a partir do esquema real da base de dados, depois de os scripts terem sido executados e testados.</t>
   </si>
   <si>
     <t>Por isso o dicionário, o diagrama e os scripts não podem divergir: saem todos da mesma fonte.</t>
@@ -39,19 +39,19 @@
     <t>Folhas deste ficheiro</t>
   </si>
   <si>
-    <t>Tabelas          — as 17 tabelas e para que serve cada uma.</t>
-  </si>
-  <si>
-    <t>Dicionário       — as 99 colunas: tipo, obrigatoriedade, chave, descrição e regras.</t>
-  </si>
-  <si>
-    <t>Ligações         — todas as chaves estrangeiras, lidas em português.</t>
-  </si>
-  <si>
-    <t>Regras           — todos os CHECK, DEFAULT e UNIQUE, com a razão de existirem.</t>
-  </si>
-  <si>
-    <t>Alterações       — as quatro mudanças pedidas pela professora e o que cada uma resolve.</t>
+    <t>Tabelas       — as 16 tabelas e a vista, e para que serve cada uma.</t>
+  </si>
+  <si>
+    <t>Dicionário    — as 89 colunas: tipo, obrigatoriedade, chave, descrição e regras.</t>
+  </si>
+  <si>
+    <t>Ligações      — as 19 chaves estrangeiras, lidas em português.</t>
+  </si>
+  <si>
+    <t>Regras        — todos os CHECK e UNIQUE, com a razão de existirem.</t>
+  </si>
+  <si>
+    <t>Alterações    — as quatro mudanças pedidas pela docente e o que cada uma resolve.</t>
   </si>
   <si>
     <t>Como ler a coluna Chave</t>
@@ -75,141 +75,144 @@
     <t>Um carregamento a decorrer tem EnergiaKwh a NULL porque a energia final ainda não existe.</t>
   </si>
   <si>
-    <t>As 17 tabelas do modelo</t>
+    <t>As 16 tabelas e a vista</t>
+  </si>
+  <si>
+    <t>Nome</t>
+  </si>
+  <si>
+    <t>Papel</t>
+  </si>
+  <si>
+    <t>Colunas</t>
+  </si>
+  <si>
+    <t>Para que serve</t>
+  </si>
+  <si>
+    <t>Concelho</t>
+  </si>
+  <si>
+    <t>Domínio</t>
+  </si>
+  <si>
+    <t>Concelhos onde a rede tem postos. Existe para o nome não ser texto livre repetido em cada posto.</t>
+  </si>
+  <si>
+    <t>TipoConector</t>
+  </si>
+  <si>
+    <t>Tipos de tomada: Type 2, CCS2, CHAdeMO, Type 1.</t>
+  </si>
+  <si>
+    <t>Posto</t>
+  </si>
+  <si>
+    <t>Principal</t>
+  </si>
+  <si>
+    <t>Cada posto de carregamento, com a sua potência e localização.</t>
+  </si>
+  <si>
+    <t>PostoConector</t>
+  </si>
+  <si>
+    <t>Ligação</t>
+  </si>
+  <si>
+    <t>Resolve o N:M entre Posto e TipoConector. Cada linha é uma tomada concreta.</t>
+  </si>
+  <si>
+    <t>TipoAvaria</t>
+  </si>
+  <si>
+    <t>Categorias de avaria usadas na manutenção.</t>
+  </si>
+  <si>
+    <t>Ocorrencia</t>
+  </si>
+  <si>
+    <t>Cada avaria participada num posto. É também o histórico de avarias da regra 3.7.</t>
+  </si>
+  <si>
+    <t>Alerta</t>
+  </si>
+  <si>
+    <t>Carregamentos em que a energia declarada excede o que o posto conseguiria entregar.</t>
+  </si>
+  <si>
+    <t>Cliente</t>
+  </si>
+  <si>
+    <t>Particulares e empresas. O mesmo cliente pode ser condutor, pagador ou ambos.</t>
+  </si>
+  <si>
+    <t>Veiculo</t>
+  </si>
+  <si>
+    <t>Viaturas elétricas associadas a um cliente.</t>
+  </si>
+  <si>
+    <t>Reserva</t>
+  </si>
+  <si>
+    <t>Marcações de uma janela de tempo num posto.</t>
+  </si>
+  <si>
+    <t>Carregamento</t>
+  </si>
+  <si>
+    <t>O evento central: energia entregue numa tomada, a um veículo, por um condutor.</t>
+  </si>
+  <si>
+    <t>CarregamentoHistorico</t>
+  </si>
+  <si>
+    <t>Histórico</t>
+  </si>
+  <si>
+    <t>Regista o estado em que o carregamento ficou, a cada alteração. Preenchida por trigger.</t>
+  </si>
+  <si>
+    <t>Fatura</t>
+  </si>
+  <si>
+    <t>Agrupa carregamentos num documento de cobrança dirigido a um pagador.</t>
+  </si>
+  <si>
+    <t>Pagamento</t>
+  </si>
+  <si>
+    <t>Entradas de dinheiro. Uma fatura pode receber vários pagamentos parciais.</t>
+  </si>
+  <si>
+    <t>Tarifario</t>
+  </si>
+  <si>
+    <t>Planos comerciais. Guarda também uma cópia do preço em vigor.</t>
+  </si>
+  <si>
+    <t>TarifarioPreco</t>
+  </si>
+  <si>
+    <t>Histórico de preços de cada tarifário, com data de início e de fim.</t>
+  </si>
+  <si>
+    <t>vw_PostosAtivos</t>
+  </si>
+  <si>
+    <t>Vista</t>
+  </si>
+  <si>
+    <t>Um SELECT guardado com um nome. Esconde o JOIN com o Concelho e o filtro dos postos ativos, para ninguém se esquecer dele. Não guarda dados.</t>
+  </si>
+  <si>
+    <t>Dicionário de dados — 89 colunas</t>
   </si>
   <si>
     <t>Tabela</t>
   </si>
   <si>
-    <t>Papel</t>
-  </si>
-  <si>
-    <t>Colunas</t>
-  </si>
-  <si>
-    <t>Para que serve</t>
-  </si>
-  <si>
-    <t>Concelho</t>
-  </si>
-  <si>
-    <t>Domínio</t>
-  </si>
-  <si>
-    <t>Lista dos concelhos onde a VoltGo tem postos. Existe para não repetir o nome do concelho em cada posto.</t>
-  </si>
-  <si>
-    <t>TipoConector</t>
-  </si>
-  <si>
-    <t>Lista dos tipos de tomada: Type 2, CCS, CHAdeMO.</t>
-  </si>
-  <si>
-    <t>Posto</t>
-  </si>
-  <si>
-    <t>Principal</t>
-  </si>
-  <si>
-    <t>Cada posto de carregamento da rede, com a sua potência e localização.</t>
-  </si>
-  <si>
-    <t>PostoConector</t>
-  </si>
-  <si>
-    <t>Ligação</t>
-  </si>
-  <si>
-    <t>Resolve o N:M entre Posto e TipoConector. Cada linha é uma tomada concreta.</t>
-  </si>
-  <si>
-    <t>TipoAvaria</t>
-  </si>
-  <si>
-    <t>Categorias de avaria usadas na manutenção.</t>
-  </si>
-  <si>
-    <t>Ocorrencia</t>
-  </si>
-  <si>
-    <t>Cada avaria participada num posto.</t>
-  </si>
-  <si>
-    <t>OcorrenciaHistorico</t>
-  </si>
-  <si>
-    <t>Histórico</t>
-  </si>
-  <si>
-    <t>Regista cada mudança de estado de uma ocorrência. Preenchida por trigger.</t>
-  </si>
-  <si>
-    <t>Alerta</t>
-  </si>
-  <si>
-    <t>NOVA. Regista carregamentos em que a energia declarada excede o que o posto conseguiria entregar.</t>
-  </si>
-  <si>
-    <t>Cliente</t>
-  </si>
-  <si>
-    <t>Particulares e empresas. O mesmo cliente pode ser condutor, pagador ou ambos.</t>
-  </si>
-  <si>
-    <t>Veiculo</t>
-  </si>
-  <si>
-    <t>Viaturas elétricas associadas a um cliente.</t>
-  </si>
-  <si>
-    <t>Reserva</t>
-  </si>
-  <si>
-    <t>Marcações de uma janela de tempo num posto.</t>
-  </si>
-  <si>
-    <t>Carregamento</t>
-  </si>
-  <si>
-    <t>O evento central do sistema: energia entregue numa tomada, a um veículo, por um condutor.</t>
-  </si>
-  <si>
-    <t>CarregamentoHistorico</t>
-  </si>
-  <si>
-    <t>Regista cada mudança de estado de um carregamento. Preenchida por trigger.</t>
-  </si>
-  <si>
-    <t>Fatura</t>
-  </si>
-  <si>
-    <t>NOVA. Agrupa carregamentos num documento de cobrança dirigido a um pagador.</t>
-  </si>
-  <si>
-    <t>Pagamento</t>
-  </si>
-  <si>
-    <t>Entradas de dinheiro. Uma fatura pode receber vários pagamentos parciais.</t>
-  </si>
-  <si>
-    <t>Tarifario</t>
-  </si>
-  <si>
-    <t>Planos comerciais. Guarda também uma cópia do preço em vigor.</t>
-  </si>
-  <si>
-    <t>TarifarioPreco</t>
-  </si>
-  <si>
-    <t>Histórico de preços de cada tarifário, com data de início e de fim.</t>
-  </si>
-  <si>
-    <t>A amarelo: tabelas novas nesta versão.</t>
-  </si>
-  <si>
-    <t>Dicionário de dados — 99 colunas</t>
-  </si>
-  <si>
     <t>Coluna</t>
   </si>
   <si>
@@ -246,9 +249,6 @@
     <t>IDENTITY(1,1) — o SQL Server numera sozinho</t>
   </si>
   <si>
-    <t>Nome</t>
-  </si>
-  <si>
     <t>NVARCHAR(60)</t>
   </si>
   <si>
@@ -273,7 +273,7 @@
     <t>NVARCHAR(40)</t>
   </si>
   <si>
-    <t>Nome do tipo de conector: Type 2, CCS, CHAdeMO.</t>
+    <t>Nome do tipo: Type 2, CCS2, CHAdeMO, Type 1.</t>
   </si>
   <si>
     <t>IDPosto</t>
@@ -354,7 +354,7 @@
     <t>IDPostoConector</t>
   </si>
   <si>
-    <t>Identificador da tomada, ou seja, do par posto + tipo de conector.</t>
+    <t>Identificador da tomada: o par posto + tipo de conector.</t>
   </si>
   <si>
     <t>FK AK</t>
@@ -437,125 +437,62 @@
     <t>NVARCHAR(15)</t>
   </si>
   <si>
-    <t>Fase do ciclo de vida da ocorrência.</t>
+    <t>Aberta, EmResolucao ou Resolvida.</t>
   </si>
   <si>
     <t>DEFAULT 'Aberta'
 CHECK: Estado='Resolvida' OR Estado='EmResolucao' OR Estado='Aberta'</t>
   </si>
   <si>
-    <t>IDOcorrenciaHistorico</t>
-  </si>
-  <si>
-    <t>Identificador da linha de histórico.</t>
-  </si>
-  <si>
-    <t>Ocorrência a que a mudança diz respeito.</t>
-  </si>
-  <si>
-    <t>Tem de existir em Ocorrencia.IDOcorrencia</t>
-  </si>
-  <si>
-    <t>DataHora</t>
-  </si>
-  <si>
-    <t>Momento da mudança de estado.</t>
+    <t>IDAlerta</t>
+  </si>
+  <si>
+    <t>Identificador do alerta.</t>
+  </si>
+  <si>
+    <t>IDCarregamento</t>
+  </si>
+  <si>
+    <t>Carregamento suspeito.</t>
+  </si>
+  <si>
+    <t>Tem de existir em Carregamento.IDCarregamento</t>
+  </si>
+  <si>
+    <t>DataDetecao</t>
+  </si>
+  <si>
+    <t>Momento em que a anomalia foi detetada.</t>
   </si>
   <si>
     <t>DEFAULT sysdatetime()</t>
   </si>
   <si>
-    <t>EstadoAnterior</t>
-  </si>
-  <si>
-    <t>Estado antes da mudança; NULL na primeira linha.</t>
-  </si>
-  <si>
-    <t>CHECK: EstadoAnterior IS NULL OR (EstadoAnterior='Resolvida' OR EstadoAnterior='EmResolucao' OR EstadoAnterior='Aberta')</t>
-  </si>
-  <si>
-    <t>EstadoNovo</t>
-  </si>
-  <si>
-    <t>Estado depois da mudança.</t>
-  </si>
-  <si>
-    <t>CHECK: EstadoNovo='Resolvida' OR EstadoNovo='EmResolucao' OR EstadoNovo='Aberta'</t>
-  </si>
-  <si>
-    <t>Observacao</t>
-  </si>
-  <si>
-    <t>NVARCHAR(200)</t>
-  </si>
-  <si>
-    <t>Nota livre sobre a mudança.</t>
-  </si>
-  <si>
-    <t>IDAlerta</t>
-  </si>
-  <si>
-    <t>Identificador do alerta.</t>
-  </si>
-  <si>
-    <t>IDCarregamento</t>
-  </si>
-  <si>
-    <t>Carregamento que despoletou o alerta.</t>
-  </si>
-  <si>
-    <t>Tem de existir em Carregamento.IDCarregamento</t>
-  </si>
-  <si>
-    <t>DataDetecao</t>
-  </si>
-  <si>
-    <t>Momento em que o sistema detetou a anomalia.</t>
-  </si>
-  <si>
-    <t>TipoAlerta</t>
-  </si>
-  <si>
-    <t>NVARCHAR(30)</t>
-  </si>
-  <si>
-    <t>Natureza da anomalia detetada.</t>
-  </si>
-  <si>
-    <t>CHECK: TipoAlerta='DuracaoImplausivel' OR TipoAlerta='EnergiaAcimaCapacidade'</t>
-  </si>
-  <si>
     <t>EnergiaRegistada</t>
   </si>
   <si>
     <t>DECIMAL(8,3)</t>
   </si>
   <si>
-    <t>Energia que o carregamento diz ter entregue, em kWh.</t>
+    <t>Energia que o carregamento diz ter entregue, em kWh. Congelada na deteção.</t>
   </si>
   <si>
     <t>EnergiaMaxima</t>
   </si>
   <si>
-    <t>Energia que o posto conseguiria entregar naquele tempo, em kWh.</t>
+    <t>Energia que o posto conseguiria entregar naquele tempo, em kWh. Congelada na deteção.</t>
   </si>
   <si>
     <t>NVARCHAR(12)</t>
   </si>
   <si>
-    <t>Situação da análise humana do alerta.</t>
+    <t>Situação da análise humana: Aberto, Justificado ou Confirmado.</t>
   </si>
   <si>
     <t>DEFAULT 'Aberto'
 CHECK: Estado='Confirmado' OR Estado='Justificado' OR Estado='Aberto'</t>
   </si>
   <si>
-    <t>NVARCHAR(300)</t>
-  </si>
-  <si>
-    <t>Nota de quem analisou o alerta.</t>
-  </si>
-  <si>
     <t>IDCliente</t>
   </si>
   <si>
@@ -580,7 +517,7 @@
     <t>TipoCliente</t>
   </si>
   <si>
-    <t>Distingue particular de empresarial.</t>
+    <t>Particular ou Empresarial.</t>
   </si>
   <si>
     <t>CHECK: TipoCliente='Empresarial' OR TipoCliente='Particular'</t>
@@ -664,7 +601,7 @@
     <t>Fim da janela reservada.</t>
   </si>
   <si>
-    <t>Situação da reserva.</t>
+    <t>Ativa, Concretizada, Cancelada ou Expirada.</t>
   </si>
   <si>
     <t>DEFAULT 'Ativa'
@@ -701,7 +638,7 @@
     <t>IDTarifario</t>
   </si>
   <si>
-    <t>Tarifário aplicado ao carregamento.</t>
+    <t>Tarifário aplicado.</t>
   </si>
   <si>
     <t>Tem de existir em Tarifario.IDTarifario</t>
@@ -711,13 +648,14 @@
   </si>
   <si>
     <t>Tem de existir em Reserva.IDReserva
+UNIQUE — não pode repetir
 UNIQUE filtrado WHERE IDReserva IS NOT NULL</t>
   </si>
   <si>
     <t>IDFatura</t>
   </si>
   <si>
-    <t>Fatura onde este carregamento foi incluído.</t>
+    <t>Fatura onde foi incluído. NULL enquanto não faturado.</t>
   </si>
   <si>
     <t>Tem de existir em Fatura.IDFatura</t>
@@ -747,7 +685,7 @@
     <t>CHECK: CustoTotal IS NULL OR CustoTotal&gt;=0</t>
   </si>
   <si>
-    <t>Fase do ciclo de vida do carregamento.</t>
+    <t>Fase do ciclo de vida: EmCurso, Terminado, Faturado ou Anulado.</t>
   </si>
   <si>
     <t>DEFAULT 'EmCurso'
@@ -757,10 +695,22 @@
     <t>IDCarregamentoHistorico</t>
   </si>
   <si>
-    <t>Carregamento a que a mudança diz respeito.</t>
-  </si>
-  <si>
-    <t>CHECK: EstadoAnterior IS NULL OR (EstadoAnterior='Anulado' OR EstadoAnterior='Faturado' OR EstadoAnterior='Terminado' OR EstadoAnterior='EmCurso')</t>
+    <t>Identificador da linha de histórico.</t>
+  </si>
+  <si>
+    <t>Carregamento a que a linha diz respeito.</t>
+  </si>
+  <si>
+    <t>DataHora</t>
+  </si>
+  <si>
+    <t>Momento em que ficou nesse estado.</t>
+  </si>
+  <si>
+    <t>EstadoNovo</t>
+  </si>
+  <si>
+    <t>Estado em que o carregamento ficou.</t>
   </si>
   <si>
     <t>CHECK: EstadoNovo='Anulado' OR EstadoNovo='Faturado' OR EstadoNovo='Terminado' OR EstadoNovo='EmCurso'</t>
@@ -772,13 +722,13 @@
     <t>Numero</t>
   </si>
   <si>
-    <t>Número comercial da fatura, no formato FT2026/0001.</t>
+    <t>Número comercial, no formato FT2026/0001.</t>
   </si>
   <si>
     <t>IDClientePagador</t>
   </si>
   <si>
-    <t>Entidade responsável pelo pagamento.</t>
+    <t>Entidade responsável pelo pagamento. Pode não ser quem carregou.</t>
   </si>
   <si>
     <t>DataEmissao</t>
@@ -802,7 +752,7 @@
     <t>CHECK: Metodo='Mensal' OR Metodo='Imediato'</t>
   </si>
   <si>
-    <t>Situação comercial da fatura.</t>
+    <t>Emitida, Paga ou Anulada.</t>
   </si>
   <si>
     <t>DEFAULT 'Emitida'
@@ -836,7 +786,7 @@
     <t>MeioPagamento</t>
   </si>
   <si>
-    <t>Como foi pago: MBWay, Cartão, Transferência.</t>
+    <t>MBWay, Cartão ou Transferência.</t>
   </si>
   <si>
     <t>Identificador do tarifário.</t>
@@ -857,7 +807,7 @@
     <t>DECIMAL(8,4)</t>
   </si>
   <si>
-    <t>Cópia do preço por kWh em vigor; mantida pelo trigger de sincronização.</t>
+    <t>Cópia do preço em vigor; mantida pelo trigger de sincronização.</t>
   </si>
   <si>
     <t>CHECK: PrecoKwhAtual IS NULL OR PrecoKwhAtual&gt;0</t>
@@ -869,7 +819,7 @@
     <t>DECIMAL(8,2)</t>
   </si>
   <si>
-    <t>Cópia da taxa de ativação em vigor; mantida pelo trigger de sincronização.</t>
+    <t>Cópia da taxa em vigor; mantida pelo trigger de sincronização.</t>
   </si>
   <si>
     <t>CHECK: TaxaAtivacaoAtual IS NULL OR TaxaAtivacaoAtual&gt;=0</t>
@@ -920,7 +870,7 @@
 CHECK: TaxaAtivacao&gt;=0</t>
   </si>
   <si>
-    <t>As 20 ligações entre tabelas</t>
+    <t>As 19 ligações entre tabelas</t>
   </si>
   <si>
     <t>Tabela com a FK</t>
@@ -1004,12 +954,6 @@
     <t>Cada avaria tem uma categoria.</t>
   </si>
   <si>
-    <t>Ocorrencia.IDOcorrencia</t>
-  </si>
-  <si>
-    <t>Cada linha de histórico pertence a uma ocorrência.</t>
-  </si>
-  <si>
     <t>Cada pagamento abate numa fatura; uma fatura recebe vários pagamentos.</t>
   </si>
   <si>
@@ -1025,7 +969,7 @@
     <t>TipoConector.IDTipoConector</t>
   </si>
   <si>
-    <t>Cada tomada é de um tipo; o mesmo tipo aparece em muitos postos.</t>
+    <t>Cada tomada é de um tipo; o mesmo tipo existe em muitos postos.</t>
   </si>
   <si>
     <t>Cada reserva é feita por um cliente.</t>
@@ -1037,10 +981,10 @@
     <t>Cada vigência de preço pertence a um tarifário.</t>
   </si>
   <si>
-    <t>Cada veículo tem um proprietário; um cliente pode ter vários veículos.</t>
-  </si>
-  <si>
-    <t>Regras de integridade — o que a base de dados recusa aceitar</t>
+    <t>Cada veículo tem um proprietário; um cliente pode ter vários.</t>
+  </si>
+  <si>
+    <t>Regras de integridade — o que a base recusa aceitar</t>
   </si>
   <si>
     <t>Nome da restrição</t>
@@ -1064,15 +1008,6 @@
     <t>O ciclo de vida do alerta é fechado: Aberto, Justificado ou Confirmado.</t>
   </si>
   <si>
-    <t>CHK_Alerta_Tipo</t>
-  </si>
-  <si>
-    <t>TipoAlerta='DuracaoImplausivel' OR TipoAlerta='EnergiaAcimaCapacidade'</t>
-  </si>
-  <si>
-    <t>Só dois tipos de anomalia estão previstos.</t>
-  </si>
-  <si>
     <t>CHK_Alerta_Valores</t>
   </si>
   <si>
@@ -1136,21 +1071,15 @@
     <t>Uma reserva concretiza-se no máximo uma vez. É filtrado porque muitos carregamentos não têm reserva, e vários NULL não são «repetidos».</t>
   </si>
   <si>
-    <t>CHK_CarregHist_Anterior</t>
-  </si>
-  <si>
-    <t>EstadoAnterior IS NULL OR (EstadoAnterior='Anulado' OR EstadoAnterior='Faturado' OR EstadoAnterior='Terminado' OR EstadoAnterior='EmCurso')</t>
+    <t>CHK_CarregHist_Novo</t>
+  </si>
+  <si>
+    <t>EstadoNovo='Anulado' OR EstadoNovo='Faturado' OR EstadoNovo='Terminado' OR EstadoNovo='EmCurso'</t>
   </si>
   <si>
     <t>O histórico só pode conter estados que existem de verdade.</t>
   </si>
   <si>
-    <t>CHK_CarregHist_Novo</t>
-  </si>
-  <si>
-    <t>EstadoNovo='Anulado' OR EstadoNovo='Faturado' OR EstadoNovo='Terminado' OR EstadoNovo='EmCurso'</t>
-  </si>
-  <si>
     <t>CHK_Cliente_Nascimento</t>
   </si>
   <si>
@@ -1175,7 +1104,7 @@
     <t>DataVencimento&gt;=DataEmissao</t>
   </si>
   <si>
-    <t>Não se pode vencer antes de ser emitida.</t>
+    <t>Não se pode vencer antes de ser emitida. O &gt;= permite pagamento no próprio dia.</t>
   </si>
   <si>
     <t>CHK_Fatura_Estado</t>
@@ -1214,18 +1143,6 @@
     <t>Lista fechada de estados.</t>
   </si>
   <si>
-    <t>CHK_OcorrHist_Anterior</t>
-  </si>
-  <si>
-    <t>EstadoAnterior IS NULL OR (EstadoAnterior='Resolvida' OR EstadoAnterior='EmResolucao' OR EstadoAnterior='Aberta')</t>
-  </si>
-  <si>
-    <t>CHK_OcorrHist_Estado</t>
-  </si>
-  <si>
-    <t>EstadoNovo='Resolvida' OR EstadoNovo='EmResolucao' OR EstadoNovo='Aberta'</t>
-  </si>
-  <si>
     <t>CHK_Pag_Valor</t>
   </si>
   <si>
@@ -1322,10 +1239,10 @@
     <t>Só pode haver um preço em vigor por tarifário ao mesmo tempo.</t>
   </si>
   <si>
-    <t>Não estão aqui os DEFAULT nem os UNIQUE simples: esses aparecem na folha Dicionário, coluna Regras.</t>
-  </si>
-  <si>
-    <t>As quatro alterações pedidas pela professora</t>
+    <t>Os DEFAULT e os UNIQUE simples aparecem na folha Dicionário, coluna Regras.</t>
+  </si>
+  <si>
+    <t>As quatro alterações pedidas pela docente</t>
   </si>
   <si>
     <t>#</t>
@@ -1349,13 +1266,13 @@
     <t>Nova entidade Fatura</t>
   </si>
   <si>
-    <t>Antes, o pagamento apontava diretamente ao carregamento e não havia forma de agrupar vários carregamentos num documento só.</t>
-  </si>
-  <si>
-    <t>Carregamento ganhou IDFatura (NULL enquanto não faturado). Pagamento passou a apontar para Fatura em vez de Carregamento.</t>
-  </si>
-  <si>
-    <t>Agora um cliente empresarial recebe uma fatura mensal com 10 carregamentos e paga em 3 prestações. Antes isso era impossível de representar.</t>
+    <t>O pagamento apontava diretamente ao carregamento. Não havia forma de agrupar vários carregamentos num documento só.</t>
+  </si>
+  <si>
+    <t>Carregamento ganhou IDFatura (NULL enquanto não faturado). Pagamento passou a apontar para Fatura.</t>
+  </si>
+  <si>
+    <t>Um cliente empresarial recebe uma fatura mensal com vários carregamentos e pode pagá-la em prestações.</t>
   </si>
   <si>
     <t>2</t>
@@ -1364,13 +1281,13 @@
     <t>Remoção do IDPosto em Carregamento</t>
   </si>
   <si>
-    <t>O carregamento guardava IDPosto e IDPostoConector ao mesmo tempo. A tomada já sabe a que posto pertence, logo era redundante.</t>
-  </si>
-  <si>
-    <t>Coluna IDPosto eliminada de Carregamento. Todas as consultas passam pelo PostoConector para chegar ao Posto.</t>
-  </si>
-  <si>
-    <t>Elimina o risco de a base de dados ficar a dizer duas coisas diferentes sobre o mesmo carregamento.</t>
+    <t>O carregamento guardava IDPosto e IDPostoConector. A tomada já sabe a que posto pertence.</t>
+  </si>
+  <si>
+    <t>Coluna IDPosto eliminada. As consultas passam pelo PostoConector para chegar ao Posto.</t>
+  </si>
+  <si>
+    <t>Elimina o risco de a base dizer duas coisas diferentes sobre o mesmo carregamento.</t>
   </si>
   <si>
     <t>3</t>
@@ -1382,10 +1299,10 @@
     <t>Consultar o preço em vigor obrigava sempre a ir à TarifarioPreco e filtrar por DataFim IS NULL.</t>
   </si>
   <si>
-    <t>Tarifario ganhou PrecoKwhAtual e TaxaAtivacaoAtual. A TarifarioPreco mantém-se como histórico e continua a ser a fonte da verdade.</t>
-  </si>
-  <si>
-    <t>O trigger TR_TarifarioPreco_SincronizaAtual copia automaticamente o preço em vigor para o Tarifario. Não é possível alterar um e esquecer o outro.</t>
+    <t>Tarifario ganhou PrecoKwhAtual e TaxaAtivacaoAtual. A TarifarioPreco mantém-se como histórico e fonte da verdade.</t>
+  </si>
+  <si>
+    <t>O trigger TR_TarifarioPreco_SincronizaAtual copia o preço automaticamente. Não é possível alterar um e esquecer o outro.</t>
   </si>
   <si>
     <t>4</t>
@@ -1394,13 +1311,13 @@
     <t>Nova funcionalidade Alerta</t>
   </si>
   <si>
-    <t>Não havia forma de detetar registos fisicamente impossíveis, como 45 kWh entregues em 1 hora por um posto de 22 kW.</t>
-  </si>
-  <si>
-    <t>Nova tabela Alerta, alimentada pelo trigger TR_Carregamento_Alerta e pela função fn_EnergiaMaxima.</t>
-  </si>
-  <si>
-    <t>O alerta não bloqueia o registo: regista a suspeita e deixa um humano classificá-la como Justificado ou Confirmado.</t>
+    <t>Não havia forma de detetar registos fisicamente impossíveis, como 45 kWh numa hora num posto de 22 kW.</t>
+  </si>
+  <si>
+    <t>Nova tabela Alerta, alimentada pela consulta do script 06.</t>
+  </si>
+  <si>
+    <t>O alerta não bloqueia o registo: regista a suspeita e deixa um humano classificá-la.</t>
   </si>
 </sst>
 </file>
@@ -1447,14 +1364,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="10"/>
-      <color rgb="FF555555"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -1474,6 +1383,14 @@
       <i/>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF555555"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1566,22 +1483,22 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1991,7 +1908,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.7109375" customWidth="1"/>
@@ -2108,80 +2025,80 @@
         <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C9" s="5">
         <v>6</v>
       </c>
       <c r="D9" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="6" t="s">
+      <c r="B10" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="5">
+        <v>8</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>41</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="6">
-        <v>8</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C12" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C13" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>29</v>
-      </c>
       <c r="C14" s="5">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>50</v>
@@ -2192,26 +2109,26 @@
         <v>51</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C15" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="6">
-        <v>7</v>
-      </c>
-      <c r="D16" s="6" t="s">
+      <c r="C16" s="5">
+        <v>5</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2234,31 +2151,26 @@
         <v>57</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="C18" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="5">
-        <v>6</v>
-      </c>
-      <c r="D19" s="5" t="s">
+      <c r="B19" s="6" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="7" t="s">
+      <c r="C19" s="6">
+        <v>5</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>61</v>
       </c>
     </row>
@@ -2269,7 +2181,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.7109375" customWidth="1"/>
@@ -2288,59 +2200,59 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="4" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E4" s="10" t="s">
-        <v>72</v>
+      <c r="D4" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -2348,15 +2260,15 @@
         <v>23</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C5" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E5" s="11" t="s">
+      <c r="D5" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>77</v>
       </c>
       <c r="F5" s="5" t="s">
@@ -2367,15 +2279,15 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="5" t="s">
@@ -2384,20 +2296,20 @@
       <c r="B7" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D7" s="9" t="s">
+      <c r="C7" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="10" t="s">
-        <v>72</v>
+      <c r="D7" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>81</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2407,13 +2319,13 @@
       <c r="B8" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D8" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" s="11" t="s">
+      <c r="D8" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>77</v>
       </c>
       <c r="F8" s="5" t="s">
@@ -2424,15 +2336,15 @@
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="5" t="s">
@@ -2441,20 +2353,20 @@
       <c r="B10" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D10" s="9" t="s">
+      <c r="C10" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E10" s="10" t="s">
-        <v>72</v>
+      <c r="D10" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>86</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2464,13 +2376,13 @@
       <c r="B11" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="D11" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E11" s="11" t="s">
+      <c r="D11" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>77</v>
       </c>
       <c r="F11" s="5" t="s">
@@ -2485,15 +2397,15 @@
         <v>28</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="C12" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="D12" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" s="11" t="s">
         <v>90</v>
       </c>
       <c r="F12" s="5" t="s">
@@ -2510,13 +2422,13 @@
       <c r="B13" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D13" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E13" s="9"/>
+      <c r="D13" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="8"/>
       <c r="F13" s="5" t="s">
         <v>95</v>
       </c>
@@ -2529,13 +2441,13 @@
       <c r="B14" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="D14" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E14" s="9"/>
+      <c r="D14" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14" s="8"/>
       <c r="F14" s="5" t="s">
         <v>98</v>
       </c>
@@ -2550,13 +2462,13 @@
       <c r="B15" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="D15" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E15" s="9"/>
+      <c r="D15" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" s="8"/>
       <c r="F15" s="5" t="s">
         <v>102</v>
       </c>
@@ -2569,13 +2481,13 @@
       <c r="B16" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="D16" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E16" s="9"/>
+      <c r="D16" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" s="8"/>
       <c r="F16" s="5" t="s">
         <v>105</v>
       </c>
@@ -2590,28 +2502,28 @@
       <c r="B17" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="E17" s="9"/>
+      <c r="E17" s="8"/>
       <c r="F17" s="5" t="s">
         <v>109</v>
       </c>
       <c r="G17" s="5"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="5" t="s">
@@ -2620,20 +2532,20 @@
       <c r="B19" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D19" s="9" t="s">
+      <c r="C19" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E19" s="10" t="s">
-        <v>72</v>
+      <c r="D19" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>111</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2643,13 +2555,13 @@
       <c r="B20" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C20" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20" s="9" t="s">
+      <c r="C20" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="D20" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" s="11" t="s">
         <v>112</v>
       </c>
       <c r="F20" s="5" t="s">
@@ -2666,13 +2578,13 @@
       <c r="B21" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C21" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D21" s="9" t="s">
+      <c r="C21" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E21" s="12" t="s">
+      <c r="D21" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E21" s="11" t="s">
         <v>112</v>
       </c>
       <c r="F21" s="5" t="s">
@@ -2683,15 +2595,15 @@
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="5" t="s">
@@ -2700,20 +2612,20 @@
       <c r="B23" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="C23" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D23" s="9" t="s">
+      <c r="C23" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E23" s="10" t="s">
-        <v>72</v>
+      <c r="D23" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>118</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2723,13 +2635,13 @@
       <c r="B24" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="D24" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E24" s="11" t="s">
+      <c r="D24" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E24" s="10" t="s">
         <v>77</v>
       </c>
       <c r="F24" s="5" t="s">
@@ -2740,15 +2652,15 @@
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="5" t="s">
@@ -2757,20 +2669,20 @@
       <c r="B26" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C26" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D26" s="9" t="s">
+      <c r="C26" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E26" s="10" t="s">
-        <v>72</v>
+      <c r="D26" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>121</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2780,13 +2692,13 @@
       <c r="B27" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D27" s="9" t="s">
+      <c r="C27" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E27" s="12" t="s">
+      <c r="D27" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E27" s="11" t="s">
         <v>90</v>
       </c>
       <c r="F27" s="5" t="s">
@@ -2803,13 +2715,13 @@
       <c r="B28" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="C28" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D28" s="9" t="s">
+      <c r="C28" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E28" s="12" t="s">
+      <c r="D28" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E28" s="11" t="s">
         <v>90</v>
       </c>
       <c r="F28" s="5" t="s">
@@ -2826,13 +2738,13 @@
       <c r="B29" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="D29" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E29" s="9"/>
+      <c r="D29" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E29" s="8"/>
       <c r="F29" s="5" t="s">
         <v>128</v>
       </c>
@@ -2845,13 +2757,13 @@
       <c r="B30" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C30" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="D30" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="E30" s="9"/>
+      <c r="E30" s="8"/>
       <c r="F30" s="5" t="s">
         <v>131</v>
       </c>
@@ -2864,13 +2776,13 @@
       <c r="B31" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="D31" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="E31" s="9"/>
+      <c r="E31" s="8"/>
       <c r="F31" s="5" t="s">
         <v>134</v>
       </c>
@@ -2885,13 +2797,13 @@
       <c r="B32" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="C32" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="D32" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E32" s="9"/>
+      <c r="D32" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E32" s="8"/>
       <c r="F32" s="5" t="s">
         <v>138</v>
       </c>
@@ -2900,15 +2812,15 @@
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="5" t="s">
@@ -2917,20 +2829,20 @@
       <c r="B34" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="C34" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D34" s="9" t="s">
+      <c r="C34" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E34" s="10" t="s">
-        <v>72</v>
+      <c r="D34" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>141</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2938,22 +2850,22 @@
         <v>38</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D35" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C35" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E35" s="12" t="s">
+      <c r="D35" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E35" s="11" t="s">
         <v>90</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2961,20 +2873,20 @@
         <v>38</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="C36" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C36" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="D36" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E36" s="9"/>
+      <c r="D36" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E36" s="8"/>
       <c r="F36" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2982,310 +2894,310 @@
         <v>38</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="E37" s="9"/>
+        <v>148</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E37" s="8"/>
       <c r="F37" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>149</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="G37" s="5"/>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="5" t="s">
         <v>38</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E38" s="9"/>
+        <v>151</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E38" s="8"/>
       <c r="F38" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="G38" s="5" t="s">
         <v>152</v>
       </c>
+      <c r="G38" s="5"/>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="5" t="s">
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C39" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="D39" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E39" s="8"/>
+      <c r="F39" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="D39" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="E39" s="9"/>
-      <c r="F39" s="5" t="s">
+      <c r="G39" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="G39" s="5"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
+      <c r="A40" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="C41" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D41" s="9" t="s">
+      <c r="C41" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E41" s="10" t="s">
-        <v>72</v>
+      <c r="D41" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>157</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C42" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="C42" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E42" s="12" t="s">
-        <v>90</v>
-      </c>
+      <c r="D42" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E42" s="8"/>
       <c r="F42" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="G42" s="5" t="s">
-        <v>160</v>
-      </c>
+      <c r="G42" s="5"/>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C43" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="C43" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E43" s="9"/>
+      <c r="D43" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>77</v>
+      </c>
       <c r="F43" s="5" t="s">
         <v>162</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>146</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="C44" s="9" t="s">
+      <c r="C44" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E44" s="8"/>
+      <c r="F44" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="D44" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E44" s="9"/>
-      <c r="F44" s="5" t="s">
+      <c r="G44" s="5" t="s">
         <v>165</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B45" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E45" s="8"/>
+      <c r="F45" s="5" t="s">
         <v>167</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E45" s="9"/>
-      <c r="F45" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="G45" s="5"/>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E46" s="8"/>
+      <c r="F46" s="5" t="s">
         <v>170</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E46" s="9"/>
-      <c r="F46" s="5" t="s">
-        <v>171</v>
       </c>
       <c r="G46" s="5"/>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="C47" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E47" s="8"/>
+      <c r="F47" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="D47" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E47" s="9"/>
-      <c r="F47" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>174</v>
-      </c>
+      <c r="G47" s="5"/>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="E48" s="9"/>
+        <v>103</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E48" s="8"/>
       <c r="F48" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="G48" s="5"/>
+        <v>173</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
-      <c r="G49" s="8"/>
+      <c r="A49" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="7"/>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="C50" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D50" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="C50" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E50" s="10" t="s">
-        <v>72</v>
+      <c r="D50" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C51" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="D51" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="C51" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E51" s="9"/>
+      <c r="D51" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E51" s="11" t="s">
+        <v>90</v>
+      </c>
       <c r="F51" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="G51" s="5"/>
+        <v>176</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="C52" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E52" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E52" s="10" t="s">
         <v>77</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="G52" s="5" t="s">
         <v>79</v>
@@ -3293,709 +3205,711 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="C53" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="D53" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E53" s="9"/>
+        <v>180</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E53" s="8"/>
       <c r="F53" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>186</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="G53" s="5"/>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="C54" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="D54" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D54" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="E54" s="9"/>
+      <c r="E54" s="8"/>
       <c r="F54" s="5" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="G54" s="5"/>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="C55" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="D55" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="E55" s="9"/>
-      <c r="F55" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="G55" s="5"/>
+      <c r="A55" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B55" s="7"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="7"/>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="C56" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="D56" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="E56" s="9"/>
+        <v>184</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E56" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="F56" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="G56" s="5"/>
+        <v>185</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C57" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D57" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="C57" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E57" s="9"/>
+      <c r="D57" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E57" s="11" t="s">
+        <v>90</v>
+      </c>
       <c r="F57" s="5" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>106</v>
+        <v>177</v>
       </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
-      <c r="G58" s="8"/>
+      <c r="A58" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E58" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C59" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D59" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E59" s="10" t="s">
-        <v>72</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E59" s="8"/>
       <c r="F59" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="G59" s="5" t="s">
-        <v>74</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="G59" s="5"/>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="C60" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D60" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E60" s="12" t="s">
-        <v>90</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E60" s="8"/>
       <c r="F60" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="G60" s="5" t="s">
-        <v>198</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="G60" s="5"/>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="C61" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="D61" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E61" s="11" t="s">
-        <v>77</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E61" s="8"/>
       <c r="F61" s="5" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>79</v>
+        <v>193</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="C62" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="D62" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="E62" s="9"/>
+        <v>194</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E62" s="8"/>
       <c r="F62" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="G62" s="5"/>
+        <v>195</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="63" spans="1:7">
-      <c r="A63" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="C63" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="D63" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="E63" s="9"/>
-      <c r="F63" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="G63" s="5"/>
+      <c r="A63" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B63" s="7"/>
+      <c r="C63" s="7"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="7"/>
+      <c r="G63" s="7"/>
     </row>
     <row r="64" spans="1:7">
-      <c r="A64" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B64" s="8"/>
-      <c r="C64" s="8"/>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="8"/>
-      <c r="G64" s="8"/>
+      <c r="A64" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E64" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="C65" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D65" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="C65" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E65" s="10" t="s">
-        <v>72</v>
+      <c r="D65" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E65" s="11" t="s">
+        <v>90</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>74</v>
+        <v>198</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B66" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E66" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="G66" s="5" t="s">
         <v>177</v>
-      </c>
-      <c r="C66" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D66" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E66" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="F66" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="G66" s="5" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C67" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D67" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="C67" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E67" s="12" t="s">
+      <c r="D67" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E67" s="11" t="s">
         <v>90</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>123</v>
+        <v>202</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="C68" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="D68" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="C68" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E68" s="9"/>
+      <c r="D68" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E68" s="11" t="s">
+        <v>90</v>
+      </c>
       <c r="F68" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="G68" s="5"/>
+        <v>204</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="C69" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="D69" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="C69" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E69" s="9"/>
+      <c r="D69" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E69" s="11" t="s">
+        <v>112</v>
+      </c>
       <c r="F69" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="G69" s="5"/>
+        <v>206</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="C70" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="D70" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C70" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E70" s="9"/>
+      <c r="D70" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E70" s="11" t="s">
+        <v>90</v>
+      </c>
       <c r="F70" s="5" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="C71" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C71" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="D71" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E71" s="9"/>
+      <c r="D71" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E71" s="8"/>
       <c r="F71" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="G71" s="5" t="s">
-        <v>146</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="G71" s="5"/>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B72" s="8"/>
-      <c r="C72" s="8"/>
-      <c r="D72" s="8"/>
+      <c r="A72" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>108</v>
+      </c>
       <c r="E72" s="8"/>
-      <c r="F72" s="8"/>
-      <c r="G72" s="8"/>
+      <c r="F72" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="G72" s="5"/>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="C73" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D73" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E73" s="10" t="s">
-        <v>72</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E73" s="8"/>
       <c r="F73" s="5" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>74</v>
+        <v>215</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C74" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D74" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E74" s="12" t="s">
-        <v>90</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E74" s="8"/>
       <c r="F74" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="G74" s="5" t="s">
         <v>218</v>
-      </c>
-      <c r="G74" s="5" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B75" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E75" s="8"/>
+      <c r="F75" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="G75" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="C75" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D75" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E75" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="F75" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="G75" s="5" t="s">
-        <v>198</v>
-      </c>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C76" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D76" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E76" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="F76" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="G76" s="5" t="s">
-        <v>223</v>
-      </c>
+      <c r="A76" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B76" s="7"/>
+      <c r="C76" s="7"/>
+      <c r="D76" s="7"/>
+      <c r="E76" s="7"/>
+      <c r="F76" s="7"/>
+      <c r="G76" s="7"/>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="C77" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D77" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="C77" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E77" s="12" t="s">
-        <v>90</v>
+      <c r="D77" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E77" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>226</v>
+        <v>75</v>
       </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="C78" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D78" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="E78" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E78" s="11" t="s">
         <v>90</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>228</v>
+        <v>144</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="C79" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D79" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="E79" s="12" t="s">
-        <v>90</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E79" s="8"/>
       <c r="F79" s="5" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>231</v>
+        <v>147</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="C80" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E80" s="9"/>
+        <v>226</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E80" s="8"/>
       <c r="F80" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="G80" s="5"/>
+        <v>227</v>
+      </c>
+      <c r="G80" s="5" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="81" spans="1:7">
-      <c r="A81" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="C81" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="D81" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="E81" s="9"/>
-      <c r="F81" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="G81" s="5"/>
+      <c r="A81" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B81" s="7"/>
+      <c r="C81" s="7"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="7"/>
+      <c r="F81" s="7"/>
+      <c r="G81" s="7"/>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="C82" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="D82" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="E82" s="9"/>
+        <v>208</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D82" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E82" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="F82" s="5" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>236</v>
+        <v>75</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="C83" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="D83" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="E83" s="9"/>
+        <v>230</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="D83" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E83" s="10" t="s">
+        <v>77</v>
+      </c>
       <c r="F83" s="5" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>239</v>
+        <v>79</v>
       </c>
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="C84" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="D84" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="C84" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E84" s="9"/>
+      <c r="D84" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E84" s="11" t="s">
+        <v>90</v>
+      </c>
       <c r="F84" s="5" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>241</v>
+        <v>177</v>
       </c>
     </row>
     <row r="85" spans="1:7">
-      <c r="A85" s="8" t="s">
+      <c r="A85" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B85" s="8"/>
-      <c r="C85" s="8"/>
-      <c r="D85" s="8"/>
+      <c r="B85" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D85" s="8" t="s">
+        <v>72</v>
+      </c>
       <c r="E85" s="8"/>
-      <c r="F85" s="8"/>
-      <c r="G85" s="8"/>
+      <c r="F85" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="G85" s="5"/>
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="5" t="s">
         <v>51</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="C86" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D86" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E86" s="10" t="s">
-        <v>72</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D86" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E86" s="8"/>
       <c r="F86" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="G86" s="5" t="s">
-        <v>74</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="G86" s="5"/>
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="5" t="s">
         <v>51</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="C87" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D87" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E87" s="12" t="s">
-        <v>90</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="D87" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E87" s="8"/>
       <c r="F87" s="5" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>160</v>
+        <v>240</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4003,622 +3917,401 @@
         <v>51</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="C88" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="D88" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E88" s="9"/>
+        <v>136</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="D88" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E88" s="8"/>
       <c r="F88" s="5" t="s">
-        <v>145</v>
+        <v>241</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>146</v>
+        <v>242</v>
       </c>
     </row>
     <row r="89" spans="1:7">
-      <c r="A89" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="C89" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="D89" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="E89" s="9"/>
-      <c r="F89" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="G89" s="5" t="s">
-        <v>244</v>
-      </c>
+      <c r="A89" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B89" s="7"/>
+      <c r="C89" s="7"/>
+      <c r="D89" s="7"/>
+      <c r="E89" s="7"/>
+      <c r="F89" s="7"/>
+      <c r="G89" s="7"/>
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="C90" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="D90" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="C90" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E90" s="9"/>
+      <c r="D90" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E90" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="F90" s="5" t="s">
-        <v>151</v>
+        <v>244</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>245</v>
+        <v>75</v>
       </c>
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="C91" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="D91" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="E91" s="9"/>
+        <v>208</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D91" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E91" s="11" t="s">
+        <v>90</v>
+      </c>
       <c r="F91" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="G91" s="5"/>
+        <v>245</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="92" spans="1:7">
-      <c r="A92" s="8" t="s">
+      <c r="A92" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B92" s="8"/>
-      <c r="C92" s="8"/>
-      <c r="D92" s="8"/>
+      <c r="B92" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="D92" s="8" t="s">
+        <v>72</v>
+      </c>
       <c r="E92" s="8"/>
-      <c r="F92" s="8"/>
-      <c r="G92" s="8"/>
+      <c r="F92" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="G92" s="5" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="5" t="s">
         <v>53</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="C93" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D93" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E93" s="10" t="s">
-        <v>72</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D93" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E93" s="8"/>
       <c r="F93" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="G93" s="5" t="s">
-        <v>74</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="G93" s="5"/>
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="5" t="s">
         <v>53</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="C94" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="D94" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E94" s="11" t="s">
-        <v>77</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="D94" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E94" s="8"/>
       <c r="F94" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="G94" s="5" t="s">
-        <v>79</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="G94" s="5"/>
     </row>
     <row r="95" spans="1:7">
-      <c r="A95" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B95" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="C95" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D95" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E95" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="F95" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="G95" s="5" t="s">
-        <v>198</v>
-      </c>
+      <c r="A95" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B95" s="7"/>
+      <c r="C95" s="7"/>
+      <c r="D95" s="7"/>
+      <c r="E95" s="7"/>
+      <c r="F95" s="7"/>
+      <c r="G95" s="7"/>
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="C96" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="D96" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="C96" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E96" s="9"/>
+      <c r="D96" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E96" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="F96" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="G96" s="5"/>
+        <v>253</v>
+      </c>
+      <c r="G96" s="5" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="C97" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="D97" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E97" s="9"/>
+        <v>19</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D97" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E97" s="10" t="s">
+        <v>77</v>
+      </c>
       <c r="F97" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="G97" s="5"/>
+      <c r="G97" s="5" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="C98" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="D98" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E98" s="9"/>
+      <c r="C98" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D98" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E98" s="8"/>
       <c r="F98" s="5" t="s">
         <v>256</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>257</v>
+        <v>106</v>
       </c>
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="C99" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="D99" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E99" s="9"/>
+        <v>257</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="D99" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E99" s="8"/>
       <c r="F99" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="100" spans="1:7">
-      <c r="A100" s="8" t="s">
+      <c r="A100" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B100" s="8"/>
-      <c r="C100" s="8"/>
-      <c r="D100" s="8"/>
+      <c r="B100" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="D100" s="8" t="s">
+        <v>108</v>
+      </c>
       <c r="E100" s="8"/>
-      <c r="F100" s="8"/>
-      <c r="G100" s="8"/>
+      <c r="F100" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="G100" s="5" t="s">
+        <v>264</v>
+      </c>
     </row>
     <row r="101" spans="1:7">
-      <c r="A101" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B101" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="C101" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D101" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E101" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="F101" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="G101" s="5" t="s">
-        <v>74</v>
-      </c>
+      <c r="A101" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B101" s="7"/>
+      <c r="C101" s="7"/>
+      <c r="D101" s="7"/>
+      <c r="E101" s="7"/>
+      <c r="F101" s="7"/>
+      <c r="G101" s="7"/>
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="C102" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D102" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="C102" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E102" s="12" t="s">
-        <v>90</v>
+      <c r="D102" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E102" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>231</v>
+        <v>75</v>
       </c>
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="C103" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="D103" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="C103" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E103" s="9"/>
+      <c r="D103" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E103" s="11" t="s">
+        <v>112</v>
+      </c>
       <c r="F103" s="5" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="C104" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="C104" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="D104" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E104" s="9"/>
+      <c r="D104" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E104" s="10" t="s">
+        <v>77</v>
+      </c>
       <c r="F104" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="G104" s="5"/>
+        <v>270</v>
+      </c>
+      <c r="G104" s="5" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="C105" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="D105" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D105" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="E105" s="9"/>
+      <c r="E105" s="8"/>
       <c r="F105" s="5" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="G105" s="5"/>
     </row>
     <row r="106" spans="1:7">
-      <c r="A106" s="8" t="s">
+      <c r="A106" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B106" s="8"/>
-      <c r="C106" s="8"/>
-      <c r="D106" s="8"/>
+      <c r="B106" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="D106" s="8" t="s">
+        <v>72</v>
+      </c>
       <c r="E106" s="8"/>
-      <c r="F106" s="8"/>
-      <c r="G106" s="8"/>
+      <c r="F106" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="G106" s="5" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="5" t="s">
         <v>57</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="C107" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D107" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E107" s="10" t="s">
-        <v>72</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="D107" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E107" s="8"/>
       <c r="F107" s="5" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7">
-      <c r="A108" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B108" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C108" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="D108" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E108" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="F108" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="G108" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7">
-      <c r="A109" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B109" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="C109" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D109" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E109" s="9"/>
-      <c r="F109" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="G109" s="5" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7">
-      <c r="A110" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B110" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="C110" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="D110" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="E110" s="9"/>
-      <c r="F110" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="G110" s="5" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7">
-      <c r="A111" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B111" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="C111" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="D111" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="E111" s="9"/>
-      <c r="F111" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="G111" s="5" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7">
-      <c r="A112" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B112" s="8"/>
-      <c r="C112" s="8"/>
-      <c r="D112" s="8"/>
-      <c r="E112" s="8"/>
-      <c r="F112" s="8"/>
-      <c r="G112" s="8"/>
-    </row>
-    <row r="113" spans="1:7">
-      <c r="A113" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B113" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="C113" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D113" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E113" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="F113" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="G113" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7">
-      <c r="A114" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B114" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="C114" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D114" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E114" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="F114" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="G114" s="5" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7">
-      <c r="A115" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B115" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="C115" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="D115" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E115" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="F115" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="G115" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7">
-      <c r="A116" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B116" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="C116" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="D116" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="E116" s="9"/>
-      <c r="F116" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="G116" s="5"/>
-    </row>
-    <row r="117" spans="1:7">
-      <c r="A117" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B117" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="C117" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="D117" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E117" s="9"/>
-      <c r="F117" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="G117" s="5" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7">
-      <c r="A118" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B118" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="C118" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="D118" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E118" s="9"/>
-      <c r="F118" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="G118" s="5" t="s">
-        <v>295</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="16">
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="A9:G9"/>
@@ -4628,14 +4321,13 @@
     <mergeCell ref="A33:G33"/>
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="A49:G49"/>
-    <mergeCell ref="A58:G58"/>
-    <mergeCell ref="A64:G64"/>
-    <mergeCell ref="A72:G72"/>
-    <mergeCell ref="A85:G85"/>
-    <mergeCell ref="A92:G92"/>
-    <mergeCell ref="A100:G100"/>
-    <mergeCell ref="A106:G106"/>
-    <mergeCell ref="A112:G112"/>
+    <mergeCell ref="A55:G55"/>
+    <mergeCell ref="A63:G63"/>
+    <mergeCell ref="A76:G76"/>
+    <mergeCell ref="A81:G81"/>
+    <mergeCell ref="A89:G89"/>
+    <mergeCell ref="A95:G95"/>
+    <mergeCell ref="A101:G101"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4643,7 +4335,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="24.7109375" customWidth="1"/>
@@ -4653,177 +4345,177 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>301</v>
+        <v>284</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>304</v>
+      <c r="A3" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>308</v>
+      <c r="A5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>110</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>311</v>
+        <v>294</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>313</v>
+        <v>296</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>314</v>
+        <v>297</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>315</v>
+        <v>298</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>316</v>
+        <v>299</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>317</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="B11" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>302</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -4834,13 +4526,13 @@
         <v>85</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>321</v>
+        <v>304</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -4851,64 +4543,64 @@
         <v>117</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>323</v>
+        <v>306</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="5" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>120</v>
+        <v>208</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>324</v>
+        <v>290</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>326</v>
+      <c r="A15" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -4916,101 +4608,84 @@
         <v>31</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>330</v>
+        <v>288</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>331</v>
+        <v>313</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>177</v>
+        <v>85</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>85</v>
+        <v>203</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>320</v>
+        <v>297</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>333</v>
+        <v>315</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>224</v>
+        <v>156</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>314</v>
+        <v>288</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>335</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -5020,461 +4695,461 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.7109375" customWidth="1"/>
     <col min="2" max="2" width="28.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" customWidth="1"/>
     <col min="4" max="4" width="58.7109375" customWidth="1"/>
     <col min="5" max="5" width="62.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>336</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>339</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>341</v>
+        <v>321</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>322</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>342</v>
+        <v>323</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>343</v>
+        <v>324</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>341</v>
+        <v>325</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>322</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>345</v>
+        <v>326</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>346</v>
+        <v>327</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>341</v>
+        <v>328</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>322</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>349</v>
+        <v>330</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>341</v>
+        <v>331</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>322</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>351</v>
+        <v>332</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>352</v>
+        <v>333</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>341</v>
+        <v>334</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>322</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>354</v>
+        <v>335</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>355</v>
+        <v>327</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>341</v>
+        <v>336</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>322</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>357</v>
+        <v>337</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="C9" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>341</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>343</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>365</v>
+        <v>346</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>322</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>366</v>
+        <v>347</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>367</v>
+        <v>348</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="5" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>341</v>
+        <v>349</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>322</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>370</v>
+        <v>351</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="5" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>341</v>
+        <v>352</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>322</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>372</v>
+        <v>353</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>370</v>
+        <v>354</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="5" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>341</v>
+        <v>355</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>322</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>375</v>
+        <v>357</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="5" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>341</v>
+        <v>358</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>322</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>379</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>341</v>
+        <v>361</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>322</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>341</v>
+        <v>364</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>322</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>341</v>
+        <v>367</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>322</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>387</v>
+        <v>369</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>341</v>
+        <v>370</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>322</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>389</v>
+        <v>371</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>391</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>341</v>
+        <v>373</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>322</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>393</v>
+        <v>375</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>341</v>
+        <v>376</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>322</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>341</v>
+        <v>379</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>322</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>397</v>
+        <v>380</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>398</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>341</v>
+        <v>381</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>322</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>399</v>
+        <v>382</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>400</v>
+        <v>383</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>401</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>341</v>
+        <v>384</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>322</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>404</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>341</v>
+        <v>387</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>322</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>341</v>
+        <v>390</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>322</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>341</v>
+        <v>393</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>322</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>410</v>
+        <v>394</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>411</v>
+        <v>395</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -5482,16 +5157,16 @@
         <v>57</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>412</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>341</v>
+        <v>396</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>322</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>413</v>
+        <v>397</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>414</v>
+        <v>398</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -5499,89 +5174,21 @@
         <v>57</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>415</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>341</v>
+        <v>399</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>343</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>416</v>
+        <v>400</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>341</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>419</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>420</v>
+        <v>401</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>421</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>341</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>422</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>424</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>341</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>425</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>427</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>365</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="7" t="s">
-        <v>430</v>
+      <c r="A31" s="12" t="s">
+        <v>402</v>
       </c>
     </row>
   </sheetData>
@@ -5602,92 +5209,92 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>431</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>432</v>
+        <v>404</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>433</v>
+        <v>405</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>434</v>
+        <v>406</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>435</v>
+        <v>407</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>436</v>
+        <v>408</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="6" t="s">
-        <v>437</v>
+        <v>409</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>438</v>
+        <v>410</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>439</v>
+        <v>411</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>440</v>
+        <v>412</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>441</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="6" t="s">
-        <v>442</v>
+        <v>414</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>443</v>
+        <v>415</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>444</v>
+        <v>416</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>445</v>
+        <v>417</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>446</v>
+        <v>418</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="6" t="s">
-        <v>447</v>
+        <v>419</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>448</v>
+        <v>420</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>449</v>
+        <v>421</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>450</v>
+        <v>422</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>451</v>
+        <v>423</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="6" t="s">
-        <v>452</v>
+        <v>424</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>454</v>
+        <v>426</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>455</v>
+        <v>427</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>456</v>
+        <v>428</v>
       </c>
     </row>
   </sheetData>
